--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="390">
   <si>
     <t>##var</t>
   </si>
@@ -95,328 +96,1102 @@
     <t>EMainType</t>
   </si>
   <si>
+    <t>主类型</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>consumable</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>treasure</t>
+  </si>
+  <si>
+    <t>宝物/贵重物</t>
+  </si>
+  <si>
+    <t>quest</t>
+  </si>
+  <si>
+    <t>任务/特殊物</t>
+  </si>
+  <si>
     <t>currency</t>
   </si>
   <si>
     <t>货币</t>
   </si>
   <si>
-    <t>equipment</t>
-  </si>
-  <si>
-    <t>头盔、护甲、背包、武器</t>
-  </si>
-  <si>
-    <t>battle_consumable</t>
-  </si>
-  <si>
-    <t>可在局内战斗中直接使用或消耗的物品</t>
-  </si>
-  <si>
-    <t>search_material</t>
-  </si>
-  <si>
-    <t>通过探索、搜索获得的基础或稀有材料</t>
-  </si>
-  <si>
-    <t>valuable_loot</t>
-  </si>
-  <si>
-    <t>高价值撤离物、可出售战利品</t>
-  </si>
-  <si>
-    <t>functional_item</t>
-  </si>
-  <si>
-    <t>钥匙、通行证、任务道具等功能型物品</t>
+    <t>misc</t>
+  </si>
+  <si>
+    <t>杂物</t>
   </si>
   <si>
     <t>ESubType</t>
   </si>
   <si>
-    <t>头盔</t>
-  </si>
-  <si>
-    <t>helmet</t>
-  </si>
-  <si>
-    <t>装备-头盔</t>
-  </si>
-  <si>
-    <t>护甲</t>
-  </si>
-  <si>
-    <t>armor</t>
-  </si>
-  <si>
-    <t>装备-护甲</t>
+    <t>细分类型</t>
+  </si>
+  <si>
+    <t>equipment_none</t>
+  </si>
+  <si>
+    <t>装备-无</t>
+  </si>
+  <si>
+    <t>weapon_sword</t>
+  </si>
+  <si>
+    <t>长剑/铁剑</t>
+  </si>
+  <si>
+    <t>weapon_dagger</t>
+  </si>
+  <si>
+    <t>短刃/匕首</t>
+  </si>
+  <si>
+    <t>weapon_blade</t>
+  </si>
+  <si>
+    <t>大刀</t>
+  </si>
+  <si>
+    <t>weapon_staff</t>
+  </si>
+  <si>
+    <t>法杖</t>
+  </si>
+  <si>
+    <t>armor_head</t>
+  </si>
+  <si>
+    <t>头部防具</t>
+  </si>
+  <si>
+    <t>armor_body</t>
+  </si>
+  <si>
+    <t>身体防具</t>
+  </si>
+  <si>
+    <t>bag</t>
+  </si>
+  <si>
+    <t>储物袋/背包</t>
+  </si>
+  <si>
+    <t>accessory</t>
+  </si>
+  <si>
+    <t>饰品</t>
+  </si>
+  <si>
+    <t>weapon_other</t>
+  </si>
+  <si>
+    <t>其他武器</t>
+  </si>
+  <si>
+    <t>consumable_none</t>
+  </si>
+  <si>
+    <t>消耗品-无</t>
+  </si>
+  <si>
+    <t>pill</t>
+  </si>
+  <si>
+    <t>丹药</t>
+  </si>
+  <si>
+    <t>element_stone</t>
+  </si>
+  <si>
+    <t>五行属性石</t>
+  </si>
+  <si>
+    <t>talisman</t>
+  </si>
+  <si>
+    <t>符箓</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>药剂/补给</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>食物</t>
+  </si>
+  <si>
+    <t>repair_tool</t>
+  </si>
+  <si>
+    <t>修理道具</t>
+  </si>
+  <si>
+    <t>scroll_consumable</t>
+  </si>
+  <si>
+    <t>一次性卷轴</t>
+  </si>
+  <si>
+    <t>material_none</t>
+  </si>
+  <si>
+    <t>材料-无</t>
+  </si>
+  <si>
+    <t>herb</t>
+  </si>
+  <si>
+    <t>灵草</t>
+  </si>
+  <si>
+    <t>spirit_fruit</t>
+  </si>
+  <si>
+    <t>灵果</t>
+  </si>
+  <si>
+    <t>ore</t>
+  </si>
+  <si>
+    <t>矿石/灵矿</t>
+  </si>
+  <si>
+    <t>monster_core</t>
+  </si>
+  <si>
+    <t>妖丹/妖兽材料</t>
+  </si>
+  <si>
+    <t>alchemy_material</t>
+  </si>
+  <si>
+    <t>炼丹辅材</t>
+  </si>
+  <si>
+    <t>breakthrough_material</t>
+  </si>
+  <si>
+    <t>突破材料</t>
+  </si>
+  <si>
+    <t>residue</t>
+  </si>
+  <si>
+    <t>药渣</t>
+  </si>
+  <si>
+    <t>wood_material</t>
+  </si>
+  <si>
+    <t>灵木/藤蔓</t>
+  </si>
+  <si>
+    <t>metal_material</t>
+  </si>
+  <si>
+    <t>灵铁/金属</t>
+  </si>
+  <si>
+    <t>treasure_none</t>
+  </si>
+  <si>
+    <t>宝物-无</t>
+  </si>
+  <si>
+    <t>gongfa_fragment</t>
+  </si>
+  <si>
+    <t>功法残卷</t>
+  </si>
+  <si>
+    <t>jade_slip</t>
+  </si>
+  <si>
+    <t>玉简</t>
+  </si>
+  <si>
+    <t>recipe_fragment</t>
+  </si>
+  <si>
+    <t>丹方碎片</t>
+  </si>
+  <si>
+    <t>artifact_fragment</t>
+  </si>
+  <si>
+    <t>法宝碎片</t>
+  </si>
+  <si>
+    <t>ancient_token</t>
+  </si>
+  <si>
+    <t>古宗信物</t>
+  </si>
+  <si>
+    <t>rare_treasure</t>
+  </si>
+  <si>
+    <t>稀有天材地宝</t>
+  </si>
+  <si>
+    <t>inheritance_item</t>
+  </si>
+  <si>
+    <t>传承物</t>
+  </si>
+  <si>
+    <t>quest_none</t>
+  </si>
+  <si>
+    <t>特殊-无</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>钥匙</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>通行令</t>
+  </si>
+  <si>
+    <t>array_flag</t>
+  </si>
+  <si>
+    <t>阵旗</t>
+  </si>
+  <si>
+    <t>array_core</t>
+  </si>
+  <si>
+    <t>阵盘/阵核</t>
+  </si>
+  <si>
+    <t>quest_token</t>
+  </si>
+  <si>
+    <t>任务信物</t>
+  </si>
+  <si>
+    <t>map_fragment</t>
+  </si>
+  <si>
+    <t>地图碎片</t>
+  </si>
+  <si>
+    <t>event_item</t>
+  </si>
+  <si>
+    <t>事件物品</t>
+  </si>
+  <si>
+    <t>currency_none</t>
+  </si>
+  <si>
+    <t>货币-无</t>
+  </si>
+  <si>
+    <t>spirit_stone_low</t>
+  </si>
+  <si>
+    <t>劣品灵石</t>
+  </si>
+  <si>
+    <t>spirit_stone_normal</t>
+  </si>
+  <si>
+    <t>下品灵石</t>
+  </si>
+  <si>
+    <t>spirit_stone_mid</t>
+  </si>
+  <si>
+    <t>中品灵石</t>
+  </si>
+  <si>
+    <t>spirit_stone_high</t>
+  </si>
+  <si>
+    <t>上品灵石</t>
+  </si>
+  <si>
+    <t>spirit_stone_top</t>
+  </si>
+  <si>
+    <t>极品灵石</t>
+  </si>
+  <si>
+    <t>sect_contribution</t>
+  </si>
+  <si>
+    <t>宗门贡献</t>
+  </si>
+  <si>
+    <t>black_market_token</t>
+  </si>
+  <si>
+    <t>黑市筹码</t>
+  </si>
+  <si>
+    <t>misc_none</t>
+  </si>
+  <si>
+    <t>杂物-无</t>
+  </si>
+  <si>
+    <t>junk</t>
+  </si>
+  <si>
+    <t>sell_only</t>
+  </si>
+  <si>
+    <t>售卖品</t>
+  </si>
+  <si>
+    <t>dismantle</t>
+  </si>
+  <si>
+    <t>可分解物</t>
+  </si>
+  <si>
+    <t>lore</t>
+  </si>
+  <si>
+    <t>文献/见闻</t>
+  </si>
+  <si>
+    <t>corpse_part</t>
+  </si>
+  <si>
+    <t>残骸/骸骨</t>
+  </si>
+  <si>
+    <t>ECardType</t>
+  </si>
+  <si>
+    <t>卡牌类型</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>攻击牌</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>防御牌</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>技能牌</t>
+  </si>
+  <si>
+    <t>gongfa</t>
+  </si>
+  <si>
+    <t>功法牌</t>
+  </si>
+  <si>
+    <t>消耗牌</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>状态牌</t>
+  </si>
+  <si>
+    <t>curse</t>
+  </si>
+  <si>
+    <t>诅咒牌</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>临时牌</t>
+  </si>
+  <si>
+    <t>EElement</t>
+  </si>
+  <si>
+    <t>五行属性</t>
+  </si>
+  <si>
+    <t>无属性</t>
+  </si>
+  <si>
+    <t>metal</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>earth</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>EEffectOwnerType</t>
+  </si>
+  <si>
+    <t>效果拥有者类型</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>卡牌</t>
+  </si>
+  <si>
+    <t>enemy_intent</t>
+  </si>
+  <si>
+    <t>敌人意图</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>enchant</t>
+  </si>
+  <si>
+    <t>附魔</t>
+  </si>
+  <si>
+    <t>功法</t>
+  </si>
+  <si>
+    <t>battle_rule</t>
+  </si>
+  <si>
+    <t>战斗规则</t>
+  </si>
+  <si>
+    <t>EEffectType</t>
+  </si>
+  <si>
+    <t>效果类型</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>gain_block</t>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>apply_status</t>
+  </si>
+  <si>
+    <t>施加状态</t>
+  </si>
+  <si>
+    <t>draw_card</t>
+  </si>
+  <si>
+    <t>抽牌</t>
+  </si>
+  <si>
+    <t>gain_ap</t>
+  </si>
+  <si>
+    <t>获得行动点</t>
+  </si>
+  <si>
+    <t>gain_mp</t>
+  </si>
+  <si>
+    <t>恢复/获得灵力</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>lose_hp</t>
+  </si>
+  <si>
+    <t>失去生命，不受护盾影响</t>
+  </si>
+  <si>
+    <t>add_card</t>
+  </si>
+  <si>
+    <t>添加卡牌</t>
+  </si>
+  <si>
+    <t>exhaust_card</t>
+  </si>
+  <si>
+    <t>消耗卡牌</t>
+  </si>
+  <si>
+    <t>discard_card</t>
+  </si>
+  <si>
+    <t>弃牌</t>
+  </si>
+  <si>
+    <t>clear_status</t>
+  </si>
+  <si>
+    <t>清除状态</t>
+  </si>
+  <si>
+    <t>modify_damage_taken</t>
+  </si>
+  <si>
+    <t>修改受到伤害</t>
+  </si>
+  <si>
+    <t>modify_damage_dealt</t>
+  </si>
+  <si>
+    <t>修改造成伤害</t>
+  </si>
+  <si>
+    <t>skip_action</t>
+  </si>
+  <si>
+    <t>跳过行动</t>
+  </si>
+  <si>
+    <t>EEffectTarget</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 效果目标</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>效果来源自己</t>
+  </si>
+  <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>selected_enemy</t>
+  </si>
+  <si>
+    <t>选择的敌人</t>
+  </si>
+  <si>
+    <t>all_enemies</t>
+  </si>
+  <si>
+    <t>所有敌人</t>
+  </si>
+  <si>
+    <t>random_enemy</t>
+  </si>
+  <si>
+    <t>随机敌人</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>全体单位</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>效果来源</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>当前目标</t>
+  </si>
+  <si>
+    <t>EIntentType</t>
+  </si>
+  <si>
+    <t>敌人意图类型</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>defend</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
+    <t>增益</t>
+  </si>
+  <si>
+    <t>debuff</t>
+  </si>
+  <si>
+    <t>减益</t>
+  </si>
+  <si>
+    <t>attack_debuff</t>
+  </si>
+  <si>
+    <t>攻击并减益</t>
+  </si>
+  <si>
+    <t>charge</t>
+  </si>
+  <si>
+    <t>蓄力</t>
+  </si>
+  <si>
+    <t>special</t>
+  </si>
+  <si>
+    <t>特殊行动</t>
+  </si>
+  <si>
+    <t>escape</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>summon</t>
+  </si>
+  <si>
+    <t>召唤</t>
+  </si>
+  <si>
+    <t>EWeaponType</t>
+  </si>
+  <si>
+    <t>武器类型</t>
+  </si>
+  <si>
+    <t>sword</t>
+  </si>
+  <si>
+    <t>dagger</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>staff</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>EDeckType</t>
+  </si>
+  <si>
+    <t>牌组类型</t>
+  </si>
+  <si>
+    <t>weapon_basic</t>
+  </si>
+  <si>
+    <t>武器基础牌组</t>
+  </si>
+  <si>
+    <t>功法牌组</t>
+  </si>
+  <si>
+    <t>消耗品牌组</t>
+  </si>
+  <si>
+    <t>事件临时牌组</t>
+  </si>
+  <si>
+    <t>debug</t>
+  </si>
+  <si>
+    <t>测试牌组</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>混合牌组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EScenarioType </t>
+  </si>
+  <si>
+    <t>战斗场景类型</t>
+  </si>
+  <si>
+    <t>Debug 测试战斗</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>普通战斗</t>
+  </si>
+  <si>
+    <t>elite</t>
+  </si>
+  <si>
+    <t>精英战斗</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>Boss 战斗</t>
+  </si>
+  <si>
+    <t>事件战斗</t>
+  </si>
+  <si>
+    <t>tutoria</t>
+  </si>
+  <si>
+    <t>教学战斗</t>
+  </si>
+  <si>
+    <t>EBlockClearTiming</t>
+  </si>
+  <si>
+    <t>护盾清除时机</t>
+  </si>
+  <si>
+    <t>owner_turn_start</t>
+  </si>
+  <si>
+    <t>自己回合开始清空</t>
+  </si>
+  <si>
+    <t>turn_end</t>
+  </si>
+  <si>
+    <t>当前行动回合结束清空</t>
+  </si>
+  <si>
+    <t>round_end</t>
+  </si>
+  <si>
+    <t>一整轮结束清空</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>不自动清空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EStatusType </t>
+  </si>
+  <si>
+    <t>状态类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 无</t>
+  </si>
+  <si>
+    <t>dot</t>
+  </si>
+  <si>
+    <t>持续伤害</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>控制</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>EStatusStackRule</t>
+  </si>
+  <si>
+    <t>状态叠加规则</t>
+  </si>
+  <si>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>层数叠加</t>
+  </si>
+  <si>
+    <t>refresh</t>
+  </si>
+  <si>
+    <t>刷新持续时间</t>
+  </si>
+  <si>
+    <t>replace</t>
+  </si>
+  <si>
+    <t>替换</t>
+  </si>
+  <si>
+    <t>max_only</t>
+  </si>
+  <si>
+    <t>取较大值</t>
+  </si>
+  <si>
+    <t>EStatusTickTiming</t>
+  </si>
+  <si>
+    <t>状态结算时机</t>
+  </si>
+  <si>
+    <t>拥有者回合开始</t>
+  </si>
+  <si>
+    <t>owner_turn_end</t>
+  </si>
+  <si>
+    <t>拥有者回合结束</t>
+  </si>
+  <si>
+    <t>before_action</t>
+  </si>
+  <si>
+    <t>行动前</t>
+  </si>
+  <si>
+    <t>after_action</t>
+  </si>
+  <si>
+    <t>行动后</t>
+  </si>
+  <si>
+    <t>before_attack</t>
+  </si>
+  <si>
+    <t>攻击前</t>
+  </si>
+  <si>
+    <t>after_attack</t>
+  </si>
+  <si>
+    <t>攻击后</t>
+  </si>
+  <si>
+    <t>before_damaged</t>
+  </si>
+  <si>
+    <t>受伤前</t>
+  </si>
+  <si>
+    <t>after_damaged</t>
+  </si>
+  <si>
+    <t>受伤后</t>
+  </si>
+  <si>
+    <t>EStatusRemoveTiming</t>
+  </si>
+  <si>
+    <t>状态移除时机</t>
+  </si>
+  <si>
+    <t>after_tick</t>
+  </si>
+  <si>
+    <t>结算后减少</t>
+  </si>
+  <si>
+    <t>回合结束减少</t>
+  </si>
+  <si>
+    <t>攻击后减少</t>
+  </si>
+  <si>
+    <t>受伤后减少</t>
+  </si>
+  <si>
+    <t>battle_end</t>
+  </si>
+  <si>
+    <t>战斗结束移除</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>手动移除</t>
+  </si>
+  <si>
+    <t>EStatusEffectMode</t>
+  </si>
+  <si>
+    <t>状态效果模式</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>固定值</t>
+  </si>
+  <si>
+    <t>per_stack</t>
+  </si>
+  <si>
+    <t>按层数计算</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t>百分比</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>标记型</t>
+  </si>
+  <si>
+    <t>EQuality</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>excellent</t>
+  </si>
+  <si>
+    <t>优秀</t>
+  </si>
+  <si>
+    <t>fine</t>
+  </si>
+  <si>
+    <t>精良</t>
+  </si>
+  <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>epic</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>legendary</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>EFuncID</t>
+  </si>
+  <si>
+    <t>功能id</t>
+  </si>
+  <si>
+    <t>push_img</t>
+  </si>
+  <si>
+    <t>拍脸推送图</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>backpack</t>
   </si>
   <si>
     <t>背包</t>
-  </si>
-  <si>
-    <t>backpack</t>
-  </si>
-  <si>
-    <t>装备-背包</t>
-  </si>
-  <si>
-    <t>武器-匕首</t>
-  </si>
-  <si>
-    <t>weapon_dagger</t>
-  </si>
-  <si>
-    <t>装备-匕首类武器</t>
-  </si>
-  <si>
-    <t>武器-手枪</t>
-  </si>
-  <si>
-    <t>weapon_pistol</t>
-  </si>
-  <si>
-    <t>装备-手枪类武器</t>
-  </si>
-  <si>
-    <t>武器-步枪</t>
-  </si>
-  <si>
-    <t>weapon_rifle</t>
-  </si>
-  <si>
-    <t>装备-步枪类武器</t>
-  </si>
-  <si>
-    <t>武器-重武器</t>
-  </si>
-  <si>
-    <t>weapon_heavy</t>
-  </si>
-  <si>
-    <t>装备-重型武器</t>
-  </si>
-  <si>
-    <t>回复药</t>
-  </si>
-  <si>
-    <t>healing_item</t>
-  </si>
-  <si>
-    <t>战斗消耗-回血类道具</t>
-  </si>
-  <si>
-    <t>护甲修理</t>
-  </si>
-  <si>
-    <t>armor_repair</t>
-  </si>
-  <si>
-    <t>战斗消耗-护甲修复类</t>
-  </si>
-  <si>
-    <t>武器修理</t>
-  </si>
-  <si>
-    <t>weapon_repair</t>
-  </si>
-  <si>
-    <t>战斗消耗-武器修理类</t>
-  </si>
-  <si>
-    <t>属性石</t>
-  </si>
-  <si>
-    <t>elemental_stone</t>
-  </si>
-  <si>
-    <t>战斗消耗-武器附魔材料</t>
-  </si>
-  <si>
-    <t>投掷物</t>
-  </si>
-  <si>
-    <t>throwable</t>
-  </si>
-  <si>
-    <t>战斗消耗-投掷类道具</t>
-  </si>
-  <si>
-    <t>普通材料</t>
-  </si>
-  <si>
-    <t>common_material</t>
-  </si>
-  <si>
-    <t>常见搜索材料</t>
-  </si>
-  <si>
-    <t>稀有材料</t>
-  </si>
-  <si>
-    <t>rare_material</t>
-  </si>
-  <si>
-    <t>稀有搜索材料</t>
-  </si>
-  <si>
-    <t>制作材料</t>
-  </si>
-  <si>
-    <t>crafting_material</t>
-  </si>
-  <si>
-    <t>用于制造、升级、合成</t>
-  </si>
-  <si>
-    <t>宝石类</t>
-  </si>
-  <si>
-    <t>gemstone</t>
-  </si>
-  <si>
-    <t>贵重品-宝石珠宝类</t>
-  </si>
-  <si>
-    <t>古董类</t>
-  </si>
-  <si>
-    <t>antique</t>
-  </si>
-  <si>
-    <t>贵重品-古代文物/古币类</t>
-  </si>
-  <si>
-    <t>情报类</t>
-  </si>
-  <si>
-    <t>intel_item</t>
-  </si>
-  <si>
-    <t>贵重品-数据、情报、芯片类</t>
-  </si>
-  <si>
-    <t>钥匙/通行证</t>
-  </si>
-  <si>
-    <t>key_item</t>
-  </si>
-  <si>
-    <t>功能物-钥匙、门禁卡、撤离通行证</t>
-  </si>
-  <si>
-    <t>ETargetType</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>被动物品或不可直接点击使用</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> self</t>
-  </si>
-  <si>
-    <t>对玩家自己使用</t>
-  </si>
-  <si>
-    <t>enemy</t>
-  </si>
-  <si>
-    <t>对敌方目标使用</t>
-  </si>
-  <si>
-    <t>scene</t>
-  </si>
-  <si>
-    <t>对场景、机关、撤离点等使用</t>
-  </si>
-  <si>
-    <t>EQuality</t>
-  </si>
-  <si>
-    <t>破损</t>
-  </si>
-  <si>
-    <t>broken</t>
-  </si>
-  <si>
-    <t>状态较差的低品质物品，通常属性偏低，出售价值低</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>common</t>
-  </si>
-  <si>
-    <t>最基础的常见品质，适合前期或基础产出</t>
-  </si>
-  <si>
-    <t>优秀</t>
-  </si>
-  <si>
-    <t>uncommon</t>
-  </si>
-  <si>
-    <t>略高于普通，属性和价值有小幅提升</t>
-  </si>
-  <si>
-    <t>精良</t>
-  </si>
-  <si>
-    <t>rare</t>
-  </si>
-  <si>
-    <t>中期常见的高于平均水平品质</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>epic</t>
-  </si>
-  <si>
-    <t>获取难度较高，价值和属性明显提升</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>legendary</t>
-  </si>
-  <si>
-    <t>高级品质，通常来自高风险区域或高阶来源</t>
-  </si>
-  <si>
-    <t>传说</t>
-  </si>
-  <si>
-    <t>mythic</t>
-  </si>
-  <si>
-    <t>顶级品质，极低概率或特殊玩法产出</t>
-  </si>
-  <si>
-    <t>EFuncID</t>
-  </si>
-  <si>
-    <t>push_img</t>
-  </si>
-  <si>
-    <t>拍脸推送图</t>
-  </si>
-  <si>
-    <t>shop</t>
-  </si>
-  <si>
-    <t>商城</t>
-  </si>
-  <si>
-    <t>shopbuy</t>
-  </si>
-  <si>
-    <t>商城购买</t>
   </si>
   <si>
     <t>home</t>
@@ -435,24 +1210,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -462,6 +1223,26 @@
       <color rgb="FF080808"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.05"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -615,7 +1396,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,6 +1406,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799676503799554"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,142 +1755,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1103,28 +1902,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1445,7 +2261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="26.875" customWidth="1"/>
@@ -1509,7 +2325,7 @@
       <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="2" t="s">
@@ -1544,7 +2360,7 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -1552,8 +2368,8 @@
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="2:12">
-      <c r="B4" t="s">
+    <row r="4" ht="15.75" spans="2:12">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="b">
@@ -1562,600 +2378,2661 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="8:12">
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" spans="8:12">
+      <c r="H5" s="6"/>
+      <c r="I5" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="9:12">
-      <c r="I6" t="s">
+      <c r="L5" s="8" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" spans="9:12">
+      <c r="I6" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="9:12">
-      <c r="I7" t="s">
+      <c r="L6" s="8" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" spans="9:12">
+      <c r="I7" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="K7" s="1">
         <v>3</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="8:12">
-      <c r="H8" s="5"/>
-      <c r="I8" s="5" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" spans="8:12">
+      <c r="H8" s="6"/>
+      <c r="I8" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="K8" s="1">
         <v>4</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="8:12">
-      <c r="H9" s="5"/>
-      <c r="I9" s="5" t="s">
+      <c r="L8" s="10" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" spans="8:12">
+      <c r="H9" s="6"/>
+      <c r="I9" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="K9" s="1">
         <v>5</v>
       </c>
-      <c r="L9" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
+      <c r="L9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="b">
+    </row>
+    <row r="10" ht="15.75" spans="8:12">
+      <c r="H10" s="6"/>
+      <c r="I10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="1">
+        <v>6</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="8:12">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="1">
+        <v>7</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" spans="2:13">
+      <c r="B12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="b">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" s="11">
+      <c r="H12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" spans="9:13">
+      <c r="I13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="1">
         <v>101</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="8:12">
-      <c r="H11" s="6" t="s">
+      <c r="L13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" spans="9:13">
+      <c r="I14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="1">
+        <v>102</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" spans="9:13">
+      <c r="I15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="1">
+        <v>103</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" spans="9:13">
+      <c r="I16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="1">
+        <v>104</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" spans="9:13">
+      <c r="I17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>105</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" spans="9:13">
+      <c r="I18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="1">
+        <v>106</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" spans="9:13">
+      <c r="I19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="1">
+        <v>107</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" spans="9:13">
+      <c r="I20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="1">
+        <v>108</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" spans="9:13">
+      <c r="I21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" s="1">
+        <v>109</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" spans="9:13">
+      <c r="I22" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="1">
+        <v>200</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" spans="9:13">
+      <c r="I23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="1">
+        <v>201</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" spans="9:13">
+      <c r="I24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="1">
+        <v>202</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" spans="9:13">
+      <c r="I25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" s="1">
+        <v>203</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" spans="9:13">
+      <c r="I26" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="1">
+        <v>204</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" spans="9:13">
+      <c r="I27" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="1">
+        <v>205</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" spans="9:13">
+      <c r="I28" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" s="1">
+        <v>206</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" spans="9:13">
+      <c r="I29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" s="1">
+        <v>207</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" spans="9:13">
+      <c r="I30" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="1">
+        <v>300</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" spans="9:13">
+      <c r="I31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K31" s="1">
+        <v>301</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" spans="9:13">
+      <c r="I32" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="1">
+        <v>302</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" spans="9:13">
+      <c r="I33" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="1">
+        <v>303</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" spans="9:13">
+      <c r="I34" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" s="1">
+        <v>304</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" spans="9:13">
+      <c r="I35" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K35" s="1">
+        <v>305</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" spans="9:13">
+      <c r="I36" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K36" s="1">
+        <v>306</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" spans="9:13">
+      <c r="I37" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K37" s="1">
+        <v>307</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="M37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" spans="9:13">
+      <c r="I38" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K38" s="1">
+        <v>308</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" spans="9:13">
+      <c r="I39" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="1">
+        <v>309</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" spans="9:13">
+      <c r="I40" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="K40" s="1">
+        <v>400</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" spans="9:13">
+      <c r="I41" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" s="1">
+        <v>401</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="M41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" spans="9:13">
+      <c r="I42" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K42" s="1">
+        <v>402</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" spans="9:13">
+      <c r="I43" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K43" s="1">
+        <v>403</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" spans="9:13">
+      <c r="I44" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K44" s="1">
+        <v>404</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" spans="9:13">
+      <c r="I45" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K45" s="1">
+        <v>405</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" spans="9:13">
+      <c r="I46" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K46" s="1">
+        <v>406</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" spans="9:13">
+      <c r="I47" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K47" s="1">
+        <v>407</v>
+      </c>
+      <c r="L47" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" spans="9:13">
+      <c r="I48" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K48" s="1">
+        <v>500</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" spans="9:13">
+      <c r="I49" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K49" s="1">
+        <v>501</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" spans="9:13">
+      <c r="I50" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K50" s="1">
+        <v>502</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" spans="9:13">
+      <c r="I51" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="K51" s="1">
+        <v>503</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="M51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" spans="9:13">
+      <c r="I52" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K52" s="1">
+        <v>504</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" spans="9:13">
+      <c r="I53" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K53" s="1">
+        <v>505</v>
+      </c>
+      <c r="L53" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="M53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="9:13">
+      <c r="I54" t="s">
+        <v>125</v>
+      </c>
+      <c r="K54" s="1">
+        <v>506</v>
+      </c>
+      <c r="L54" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="M54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" spans="9:13">
+      <c r="I55" t="s">
+        <v>127</v>
+      </c>
+      <c r="K55" s="1">
+        <v>507</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" spans="9:13">
+      <c r="I56" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K56" s="1">
+        <v>600</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" spans="9:13">
+      <c r="I57" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K57" s="1">
+        <v>601</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="M57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" spans="9:13">
+      <c r="I58" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="K58" s="1">
+        <v>602</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="M58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" spans="9:13">
+      <c r="I59" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K59" s="1">
+        <v>603</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="M59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" spans="9:13">
+      <c r="I60" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="K60" s="1">
+        <v>604</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="M60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" spans="9:13">
+      <c r="I61" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K61" s="1">
+        <v>605</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="M61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" spans="9:13">
+      <c r="I62" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="K62" s="1">
+        <v>606</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="M62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" spans="9:13">
+      <c r="I63" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="K63" s="1">
+        <v>607</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="M63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" spans="9:13">
+      <c r="I64" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="K64" s="1">
+        <v>700</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" spans="9:13">
+      <c r="I65" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="K65" s="1">
+        <v>701</v>
+      </c>
+      <c r="L65" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="11">
-        <v>102</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="8:12">
-      <c r="H12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="11">
-        <v>103</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="8:12">
-      <c r="H13" s="6" t="s">
+      <c r="M65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" spans="9:13">
+      <c r="I66" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="K66" s="1">
+        <v>702</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="M66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" spans="9:13">
+      <c r="I67" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K67" s="1">
+        <v>703</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="M67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" spans="9:13">
+      <c r="I68" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="K68" s="1">
+        <v>704</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="M68">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" spans="9:13">
+      <c r="I69" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="K69" s="1">
+        <v>705</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="M69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="B70" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>157</v>
+      </c>
+      <c r="I70" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" spans="9:12">
+      <c r="I71" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" spans="2:12">
+      <c r="B72" s="14"/>
+      <c r="I72" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K72" s="1">
+        <v>2</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" spans="2:12">
+      <c r="B73" s="15"/>
+      <c r="I73" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K73" s="1">
+        <v>3</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" spans="2:12">
+      <c r="B74" s="14"/>
+      <c r="I74" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K74" s="1">
+        <v>4</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12">
+      <c r="B75" s="14"/>
+      <c r="I75" t="s">
+        <v>27</v>
+      </c>
+      <c r="K75" s="1">
+        <v>5</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" spans="2:12">
+      <c r="B76" s="14"/>
+      <c r="I76" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="K76" s="1">
+        <v>6</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" spans="2:12">
+      <c r="B77" s="14"/>
+      <c r="I77" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="K77" s="1">
+        <v>7</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" spans="2:12">
+      <c r="B78" s="14"/>
+      <c r="I78" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K78" s="1">
+        <v>8</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" spans="2:12">
+      <c r="B79" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>174</v>
+      </c>
+      <c r="I79" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" spans="2:12">
+      <c r="B80" s="16"/>
+      <c r="I80" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K80" s="1">
+        <v>1</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="2:12">
+      <c r="B81" s="16"/>
+      <c r="I81" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="K81" s="1">
+        <v>2</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" spans="2:12">
+      <c r="B82" s="16"/>
+      <c r="I82" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="K82" s="1">
+        <v>3</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" spans="2:12">
+      <c r="B83" s="16"/>
+      <c r="I83" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" spans="2:12">
+      <c r="B84" s="16"/>
+      <c r="I84" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="K84" s="1">
+        <v>5</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12">
+      <c r="B85" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>187</v>
+      </c>
+      <c r="I85" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" spans="2:12">
+      <c r="B86" s="16"/>
+      <c r="I86" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="K86" s="1">
+        <v>1</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" spans="2:12">
+      <c r="B87" s="16"/>
+      <c r="I87" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="K87" s="1">
+        <v>2</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" spans="2:12">
+      <c r="B88" s="16"/>
+      <c r="I88" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="K88" s="1">
+        <v>3</v>
+      </c>
+      <c r="L88" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" spans="2:12">
+      <c r="B89" s="16"/>
+      <c r="I89" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" spans="2:12">
+      <c r="B90" s="16"/>
+      <c r="I90" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="K90" s="1">
+        <v>5</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" spans="2:12">
+      <c r="B91" s="16"/>
+      <c r="I91" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K91" s="1">
+        <v>6</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" spans="2:12">
+      <c r="B92" s="16"/>
+      <c r="I92" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="K92" s="1">
+        <v>7</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" spans="2:12">
+      <c r="B93" s="16"/>
+      <c r="I93" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="K93" s="1">
+        <v>8</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" spans="2:12">
+      <c r="B94" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>203</v>
+      </c>
+      <c r="I94" t="s">
+        <v>23</v>
+      </c>
+      <c r="K94" s="1">
+        <v>0</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" spans="2:12">
+      <c r="B95" s="16"/>
+      <c r="I95" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="K95" s="1">
+        <v>1</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" spans="2:12">
+      <c r="B96" s="16"/>
+      <c r="I96" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K96" s="1">
+        <v>2</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" spans="2:12">
+      <c r="B97" s="16"/>
+      <c r="I97" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="K97" s="1">
+        <v>3</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" spans="2:12">
+      <c r="B98" s="16"/>
+      <c r="I98" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" spans="2:12">
+      <c r="B99" s="16"/>
+      <c r="I99" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K99" s="1">
+        <v>5</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" spans="2:12">
+      <c r="B100" s="16"/>
+      <c r="I100" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="K100" s="1">
+        <v>6</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" spans="2:12">
+      <c r="B101" s="16"/>
+      <c r="I101" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K101" s="1">
+        <v>7</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" spans="2:12">
+      <c r="B102" s="16"/>
+      <c r="I102" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="K102" s="1">
+        <v>8</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" spans="2:12">
+      <c r="B103" s="16"/>
+      <c r="I103" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="K103" s="1">
+        <v>9</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" spans="2:12">
+      <c r="B104" s="16"/>
+      <c r="I104" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K104" s="1">
+        <v>10</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" spans="2:12">
+      <c r="B105" s="16"/>
+      <c r="I105" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="K105" s="1">
+        <v>11</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" spans="2:12">
+      <c r="B106" s="16"/>
+      <c r="I106" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="K106" s="1">
+        <v>12</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" spans="2:12">
+      <c r="B107" s="16"/>
+      <c r="I107" t="s">
+        <v>228</v>
+      </c>
+      <c r="K107" s="1">
+        <v>13</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" spans="2:12">
+      <c r="B108" s="16"/>
+      <c r="I108" t="s">
+        <v>230</v>
+      </c>
+      <c r="K108" s="1">
+        <v>14</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" spans="2:12">
+      <c r="B109" s="16"/>
+      <c r="I109" t="s">
+        <v>232</v>
+      </c>
+      <c r="K109" s="1">
+        <v>15</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" spans="2:12">
+      <c r="B110" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" t="b">
+        <v>0</v>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+      <c r="H110" t="s">
+        <v>235</v>
+      </c>
+      <c r="I110" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" s="1">
+        <v>0</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" spans="2:12">
+      <c r="B111" s="16"/>
+      <c r="I111" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="K111" s="1">
+        <v>1</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" spans="2:12">
+      <c r="B112" s="16"/>
+      <c r="I112" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="K112" s="1">
+        <v>2</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" spans="2:12">
+      <c r="B113" s="16"/>
+      <c r="I113" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K113" s="1">
+        <v>3</v>
+      </c>
+      <c r="L113" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" spans="2:12">
+      <c r="B114" s="16"/>
+      <c r="I114" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="K114" s="1">
+        <v>4</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" spans="2:12">
+      <c r="B115" s="16"/>
+      <c r="I115" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="K115" s="1">
+        <v>5</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" spans="2:12">
+      <c r="B116" s="16"/>
+      <c r="I116" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="K116" s="1">
+        <v>6</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" spans="2:12">
+      <c r="B117" s="16"/>
+      <c r="I117" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="K117" s="1">
+        <v>7</v>
+      </c>
+      <c r="L117" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" spans="2:12">
+      <c r="B118" s="16"/>
+      <c r="I118" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="K118" s="1">
+        <v>8</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" spans="2:12">
+      <c r="B119" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C119" t="b">
+        <v>0</v>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="H119" t="s">
+        <v>253</v>
+      </c>
+      <c r="I119" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" s="1">
+        <v>0</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" spans="2:12">
+      <c r="B120" s="16"/>
+      <c r="I120" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K120" s="1">
+        <v>1</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" spans="2:12">
+      <c r="B121" s="16"/>
+      <c r="I121" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="K121" s="1">
+        <v>2</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" spans="2:12">
+      <c r="B122" s="16"/>
+      <c r="I122" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K122" s="1">
+        <v>3</v>
+      </c>
+      <c r="L122" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" spans="2:12">
+      <c r="B123" s="16"/>
+      <c r="I123" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="K123" s="1">
+        <v>4</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" spans="2:12">
+      <c r="B124" s="16"/>
+      <c r="I124" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="K124" s="1">
+        <v>5</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" spans="2:12">
+      <c r="B125" s="16"/>
+      <c r="I125" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K125" s="1">
+        <v>6</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" spans="2:12">
+      <c r="B126" s="16"/>
+      <c r="I126" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K126" s="1">
+        <v>7</v>
+      </c>
+      <c r="L126" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" spans="2:12">
+      <c r="B127" s="16"/>
+      <c r="I127" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="K127" s="1">
+        <v>8</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" spans="2:12">
+      <c r="B128" s="16"/>
+      <c r="I128" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="K128" s="1">
+        <v>9</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" spans="2:12">
+      <c r="B129" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H129" t="s">
+        <v>272</v>
+      </c>
+      <c r="I129" t="s">
+        <v>23</v>
+      </c>
+      <c r="K129" s="1">
+        <v>0</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" spans="2:12">
+      <c r="B130" s="16"/>
+      <c r="I130" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="K130" s="1">
+        <v>1</v>
+      </c>
+      <c r="L130" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="11">
-        <v>104</v>
-      </c>
-      <c r="L13" s="6" t="s">
+    </row>
+    <row r="131" ht="15.75" spans="2:12">
+      <c r="B131" s="16"/>
+      <c r="I131" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="K131" s="1">
+        <v>2</v>
+      </c>
+      <c r="L131" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="8:12">
-      <c r="H14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="6" t="s">
+    <row r="132" ht="15.75" spans="2:12">
+      <c r="B132" s="16"/>
+      <c r="I132" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="K132" s="1">
+        <v>3</v>
+      </c>
+      <c r="L132" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="11">
-        <v>105</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="8:12">
-      <c r="H15" s="6" t="s">
+    </row>
+    <row r="133" ht="15.75" spans="2:12">
+      <c r="B133" s="16"/>
+      <c r="I133" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="K133" s="1">
+        <v>4</v>
+      </c>
+      <c r="L133" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K15" s="11">
-        <v>106</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="8:12">
-      <c r="H16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K16" s="11">
-        <v>107</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="8:12">
-      <c r="H17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="11">
-        <v>201</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="8:12">
-      <c r="H18" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" s="6" t="s">
+    </row>
+    <row r="134" ht="15.75" spans="2:12">
+      <c r="B134" s="16"/>
+      <c r="I134" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="K134" s="1">
+        <v>99</v>
+      </c>
+      <c r="L134" t="s">
         <v>60</v>
       </c>
-      <c r="K18" s="11">
-        <v>202</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="8:12">
-      <c r="H19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="11">
-        <v>203</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="8:12">
-      <c r="H20" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" s="11">
-        <v>204</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="8:12">
-      <c r="H21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" s="11">
-        <v>205</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="8:12">
-      <c r="H22" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K22" s="11">
+    </row>
+    <row r="135" spans="2:12">
+      <c r="B135" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C135" t="b">
+        <v>0</v>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+      <c r="H135" t="s">
+        <v>279</v>
+      </c>
+      <c r="I135" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" s="1">
+        <v>0</v>
+      </c>
+      <c r="L135" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" spans="2:12">
+      <c r="B136" s="16"/>
+      <c r="I136" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="K136" s="1">
+        <v>1</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" spans="2:12">
+      <c r="B137" s="16"/>
+      <c r="I137" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K137" s="1">
+        <v>2</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" spans="2:12">
+      <c r="B138" s="16"/>
+      <c r="I138" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K138" s="1">
+        <v>3</v>
+      </c>
+      <c r="L138" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" spans="2:12">
+      <c r="B139" s="16"/>
+      <c r="I139" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K139" s="1">
+        <v>4</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" spans="2:12">
+      <c r="B140" s="16"/>
+      <c r="I140" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K140" s="1">
+        <v>5</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" spans="2:12">
+      <c r="B141" s="16"/>
+      <c r="I141" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="K141" s="1">
+        <v>6</v>
+      </c>
+      <c r="L141" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="142" spans="2:12">
+      <c r="B142" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C142" t="b">
+        <v>0</v>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
+      </c>
+      <c r="H142" t="s">
+        <v>290</v>
+      </c>
+      <c r="I142" t="s">
+        <v>23</v>
+      </c>
+      <c r="K142" s="1">
+        <v>0</v>
+      </c>
+      <c r="L142" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" spans="2:12">
+      <c r="B143" s="16"/>
+      <c r="I143" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K143" s="1">
+        <v>1</v>
+      </c>
+      <c r="L143" s="8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" spans="2:12">
+      <c r="B144" s="16"/>
+      <c r="I144" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K144" s="1">
+        <v>2</v>
+      </c>
+      <c r="L144" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" spans="2:12">
+      <c r="B145" s="16"/>
+      <c r="I145" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K145" s="1">
+        <v>3</v>
+      </c>
+      <c r="L145" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" spans="2:12">
+      <c r="B146" s="16"/>
+      <c r="I146" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="K146" s="1">
+        <v>4</v>
+      </c>
+      <c r="L146" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" spans="2:12">
+      <c r="B147" s="16"/>
+      <c r="I147" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="K147" s="1">
+        <v>5</v>
+      </c>
+      <c r="L147" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" spans="2:12">
+      <c r="B148" s="16"/>
+      <c r="I148" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="K148" s="1">
+        <v>6</v>
+      </c>
+      <c r="L148" s="8" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12">
+      <c r="B149" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="8:12">
-      <c r="H23" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K23" s="11">
+      <c r="C149" t="b">
+        <v>0</v>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
         <v>302</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="8:12">
-      <c r="H24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" s="11">
+      <c r="I149" t="s">
+        <v>23</v>
+      </c>
+      <c r="K149" s="1">
+        <v>0</v>
+      </c>
+      <c r="L149" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" spans="2:12">
+      <c r="B150" s="16"/>
+      <c r="I150" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="8:12">
-      <c r="H25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K25" s="11">
-        <v>401</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="8:12">
-      <c r="H26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K26" s="11">
-        <v>402</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="8:12">
-      <c r="H27" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K27" s="11">
-        <v>403</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="8:12">
-      <c r="H28" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K28" s="11">
-        <v>501</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="b">
+      <c r="K150" s="1">
+        <v>1</v>
+      </c>
+      <c r="L150" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" spans="2:12">
+      <c r="B151" s="16"/>
+      <c r="I151" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="K151" s="1">
+        <v>2</v>
+      </c>
+      <c r="L151" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" spans="2:12">
+      <c r="B152" s="16"/>
+      <c r="I152" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="K152" s="1">
+        <v>3</v>
+      </c>
+      <c r="L152" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" spans="2:12">
+      <c r="B153" s="16"/>
+      <c r="I153" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="K153" s="1">
+        <v>4</v>
+      </c>
+      <c r="L153" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="2:12">
+      <c r="B154" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" t="b">
         <v>0</v>
       </c>
-      <c r="D29" t="b">
+      <c r="D154" t="b">
         <v>1</v>
       </c>
-      <c r="I29" t="s">
-        <v>93</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="H154" t="s">
+        <v>312</v>
+      </c>
+      <c r="I154" t="s">
+        <v>23</v>
+      </c>
+      <c r="K154" s="1">
         <v>0</v>
       </c>
-      <c r="L29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" spans="9:12">
-      <c r="I30" t="s">
-        <v>95</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="L154" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" spans="2:12">
+      <c r="B155" s="16"/>
+      <c r="I155" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K155" s="1">
         <v>1</v>
       </c>
-      <c r="L30" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" spans="9:12">
-      <c r="I31" t="s">
-        <v>97</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="L155" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" spans="2:12">
+      <c r="B156" s="16"/>
+      <c r="I156" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="K156" s="1">
         <v>2</v>
       </c>
-      <c r="L31" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="9:12">
-      <c r="I32" t="s">
-        <v>99</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="L156" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" spans="2:12">
+      <c r="B157" s="16"/>
+      <c r="I157" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="K157" s="1">
         <v>3</v>
       </c>
-      <c r="L32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" ht="28.5" spans="2:12">
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="b">
+      <c r="L157" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" spans="2:12">
+      <c r="B158" s="16"/>
+      <c r="I158" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K158" s="1">
+        <v>4</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" spans="2:12">
+      <c r="B159" s="16"/>
+      <c r="I159" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K159" s="1">
+        <v>5</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12">
+      <c r="B160" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C160" t="b">
         <v>0</v>
       </c>
-      <c r="D33" t="b">
+      <c r="D160" t="b">
         <v>1</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K33" s="11">
+      <c r="H160" t="s">
+        <v>320</v>
+      </c>
+      <c r="I160" t="s">
+        <v>23</v>
+      </c>
+      <c r="K160" s="1">
+        <v>0</v>
+      </c>
+      <c r="L160" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" spans="2:12">
+      <c r="B161" s="16"/>
+      <c r="I161" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="K161" s="1">
         <v>1</v>
       </c>
-      <c r="L33" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" ht="28.5" spans="8:12">
-      <c r="H34" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K34" s="11">
+      <c r="L161" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" spans="2:12">
+      <c r="B162" s="16"/>
+      <c r="I162" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="K162" s="1">
         <v>2</v>
       </c>
-      <c r="L34" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="8:12">
-      <c r="H35" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K35" s="11">
+      <c r="L162" s="8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" spans="2:12">
+      <c r="B163" s="16"/>
+      <c r="I163" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="K163" s="1">
         <v>3</v>
       </c>
-      <c r="L35" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="8:12">
-      <c r="H36" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="K36" s="11">
+      <c r="L163" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" spans="2:12">
+      <c r="B164" s="16"/>
+      <c r="I164" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="K164" s="1">
         <v>4</v>
       </c>
-      <c r="L36" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="8:12">
-      <c r="H37" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K37" s="11">
+      <c r="L164" s="8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="165" spans="2:12">
+      <c r="B165" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C165" t="b">
+        <v>0</v>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
+      </c>
+      <c r="H165" t="s">
+        <v>330</v>
+      </c>
+      <c r="I165" t="s">
+        <v>23</v>
+      </c>
+      <c r="K165" s="1">
+        <v>0</v>
+      </c>
+      <c r="L165" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" spans="2:12">
+      <c r="B166" s="16"/>
+      <c r="I166" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="K166" s="1">
+        <v>1</v>
+      </c>
+      <c r="L166" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" spans="2:12">
+      <c r="B167" s="16"/>
+      <c r="I167" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="K167" s="1">
+        <v>2</v>
+      </c>
+      <c r="L167" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" spans="2:12">
+      <c r="B168" s="16"/>
+      <c r="I168" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K168" s="1">
+        <v>3</v>
+      </c>
+      <c r="L168" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" spans="2:12">
+      <c r="B169" s="16"/>
+      <c r="I169" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K169" s="1">
+        <v>4</v>
+      </c>
+      <c r="L169" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" spans="2:12">
+      <c r="B170" s="16"/>
+      <c r="I170" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="K170" s="1">
         <v>5</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" ht="28.5" spans="8:12">
-      <c r="H38" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="K38" s="11">
+      <c r="L170" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" spans="2:12">
+      <c r="B171" s="16"/>
+      <c r="I171" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="K171" s="1">
         <v>6</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="39" spans="8:12">
-      <c r="H39" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="K39" s="11">
+      <c r="L171" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" spans="2:12">
+      <c r="B172" s="16"/>
+      <c r="I172" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="K172" s="1">
         <v>7</v>
       </c>
-      <c r="L39" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" t="b">
+      <c r="L172" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" spans="2:12">
+      <c r="B173" s="16"/>
+      <c r="I173" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="K173" s="1">
+        <v>8</v>
+      </c>
+      <c r="L173" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="174" spans="2:12">
+      <c r="B174" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C174" t="b">
         <v>0</v>
       </c>
-      <c r="D40" t="b">
+      <c r="D174" t="b">
         <v>1</v>
       </c>
-      <c r="I40" t="s">
-        <v>93</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="H174" t="s">
+        <v>347</v>
+      </c>
+      <c r="I174" t="s">
+        <v>23</v>
+      </c>
+      <c r="K174" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="9:12">
-      <c r="I41" t="s">
-        <v>124</v>
-      </c>
-      <c r="K41" s="1">
+      <c r="L174" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="175" spans="2:12">
+      <c r="B175" s="16"/>
+      <c r="I175" t="s">
+        <v>348</v>
+      </c>
+      <c r="K175">
         <v>1</v>
       </c>
-      <c r="L41" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="9:12">
-      <c r="I42" t="s">
-        <v>126</v>
-      </c>
-      <c r="K42" s="1">
+      <c r="L175" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176" spans="2:12">
+      <c r="B176" s="16"/>
+      <c r="I176" t="s">
+        <v>305</v>
+      </c>
+      <c r="K176">
+        <v>2</v>
+      </c>
+      <c r="L176" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="177" spans="2:12">
+      <c r="B177" s="16"/>
+      <c r="I177" t="s">
+        <v>340</v>
+      </c>
+      <c r="K177">
+        <v>3</v>
+      </c>
+      <c r="L177" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="178" spans="2:12">
+      <c r="B178" s="16"/>
+      <c r="I178" t="s">
+        <v>344</v>
+      </c>
+      <c r="K178">
+        <v>4</v>
+      </c>
+      <c r="L178" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="179" spans="2:12">
+      <c r="B179" s="16"/>
+      <c r="I179" t="s">
+        <v>353</v>
+      </c>
+      <c r="K179">
+        <v>5</v>
+      </c>
+      <c r="L179" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="180" spans="2:12">
+      <c r="B180" s="16"/>
+      <c r="I180" t="s">
+        <v>355</v>
+      </c>
+      <c r="K180">
+        <v>6</v>
+      </c>
+      <c r="L180" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="181" spans="2:12">
+      <c r="B181" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C181" t="b">
+        <v>0</v>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>358</v>
+      </c>
+      <c r="I181" t="s">
+        <v>23</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="182" spans="2:12">
+      <c r="B182" s="16"/>
+      <c r="I182" t="s">
+        <v>359</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="183" spans="2:12">
+      <c r="B183" s="16"/>
+      <c r="I183" t="s">
+        <v>361</v>
+      </c>
+      <c r="K183">
+        <v>2</v>
+      </c>
+      <c r="L183" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="184" spans="2:12">
+      <c r="B184" s="16"/>
+      <c r="I184" t="s">
+        <v>363</v>
+      </c>
+      <c r="K184">
+        <v>3</v>
+      </c>
+      <c r="L184" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="185" spans="2:12">
+      <c r="B185" s="16"/>
+      <c r="I185" t="s">
+        <v>365</v>
+      </c>
+      <c r="K185">
+        <v>4</v>
+      </c>
+      <c r="L185" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="186" spans="2:12">
+      <c r="B186" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C186" t="b">
+        <v>0</v>
+      </c>
+      <c r="D186" t="b">
+        <v>1</v>
+      </c>
+      <c r="H186" t="s">
+        <v>368</v>
+      </c>
+      <c r="I186" t="s">
+        <v>23</v>
+      </c>
+      <c r="K186" s="1">
+        <v>0</v>
+      </c>
+      <c r="L186" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" spans="2:12">
+      <c r="B187" s="16"/>
+      <c r="I187" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K187" s="1">
+        <v>1</v>
+      </c>
+      <c r="L187" s="8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" spans="2:12">
+      <c r="B188" s="16"/>
+      <c r="I188" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="K188" s="1">
+        <v>2</v>
+      </c>
+      <c r="L188" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" spans="2:12">
+      <c r="B189" s="16"/>
+      <c r="I189" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="K189" s="1">
+        <v>3</v>
+      </c>
+      <c r="L189" s="8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" spans="2:12">
+      <c r="B190" s="16"/>
+      <c r="I190" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="K190" s="1">
+        <v>4</v>
+      </c>
+      <c r="L190" s="8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" spans="2:12">
+      <c r="B191" s="16"/>
+      <c r="I191" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="K191" s="1">
+        <v>5</v>
+      </c>
+      <c r="L191" s="8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" spans="2:12">
+      <c r="B192" s="16"/>
+      <c r="I192" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="K192" s="1">
+        <v>6</v>
+      </c>
+      <c r="L192" s="8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="193" spans="2:12">
+      <c r="B193" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C193" t="b">
+        <v>0</v>
+      </c>
+      <c r="D193" t="b">
+        <v>1</v>
+      </c>
+      <c r="H193" t="s">
+        <v>381</v>
+      </c>
+      <c r="I193" t="s">
+        <v>23</v>
+      </c>
+      <c r="K193" s="1">
+        <v>0</v>
+      </c>
+      <c r="L193" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="194" spans="9:12">
+      <c r="I194" t="s">
+        <v>382</v>
+      </c>
+      <c r="K194" s="1">
+        <v>1</v>
+      </c>
+      <c r="L194" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="195" spans="9:12">
+      <c r="I195" t="s">
+        <v>384</v>
+      </c>
+      <c r="K195" s="1">
         <v>101001</v>
       </c>
-      <c r="L42" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="9:12">
-      <c r="I43" t="s">
-        <v>128</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1010012</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="9:12">
-      <c r="I44" t="s">
-        <v>42</v>
-      </c>
-      <c r="K44" s="1">
+      <c r="L195" s="9" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="196" spans="9:12">
+      <c r="I196" t="s">
+        <v>386</v>
+      </c>
+      <c r="K196" s="1">
         <v>101002</v>
       </c>
-      <c r="L44" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="9:12">
-      <c r="I45" t="s">
-        <v>130</v>
-      </c>
-      <c r="K45" s="1">
+      <c r="L196" s="9" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="197" spans="9:12">
+      <c r="I197" t="s">
+        <v>388</v>
+      </c>
+      <c r="K197" s="1">
         <v>101003</v>
       </c>
-      <c r="L45" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="8:12">
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="L46" s="13"/>
-    </row>
-    <row r="47" ht="15.75" spans="8:12">
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="L47" s="14"/>
-    </row>
-    <row r="48" ht="15.75" spans="12:12">
-      <c r="L48" s="14"/>
-    </row>
-    <row r="49" ht="15.75" spans="12:12">
-      <c r="L49" s="14"/>
-    </row>
-    <row r="50" ht="15.75" spans="12:12">
-      <c r="L50" s="14"/>
+      <c r="L197" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="198" spans="8:12">
+      <c r="H198" s="17"/>
+      <c r="I198" s="17"/>
+      <c r="L198" s="18"/>
+    </row>
+    <row r="199" ht="15.75" spans="8:12">
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="L199" s="19"/>
+    </row>
+    <row r="200" ht="15.75" spans="12:12">
+      <c r="L200" s="19"/>
+    </row>
+    <row r="201" ht="15.75" spans="12:12">
+      <c r="L201" s="19"/>
+    </row>
+    <row r="202" ht="15.75" spans="12:12">
+      <c r="L202" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2165,4 +5042,15 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -927,7 +927,7 @@
     <t>事件战斗</t>
   </si>
   <si>
-    <t>tutoria</t>
+    <t>tutorial</t>
   </si>
   <si>
     <t>教学战斗</t>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="397">
   <si>
     <t>##var</t>
   </si>
@@ -624,7 +624,7 @@
     <t>enchant</t>
   </si>
   <si>
-    <t>附魔</t>
+    <t>注灵</t>
   </si>
   <si>
     <t>功法</t>
@@ -1170,16 +1170,37 @@
     <t>传说</t>
   </si>
   <si>
+    <t>EPurityGrade</t>
+  </si>
+  <si>
+    <t>属性石纯度</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>劣质纯度</t>
+  </si>
+  <si>
+    <t>普通纯度</t>
+  </si>
+  <si>
+    <t>refined</t>
+  </si>
+  <si>
+    <t>精纯纯度</t>
+  </si>
+  <si>
+    <t>flawless</t>
+  </si>
+  <si>
+    <t>无瑕纯度</t>
+  </si>
+  <si>
     <t>EFuncID</t>
   </si>
   <si>
     <t>功能id</t>
-  </si>
-  <si>
-    <t>push_img</t>
-  </si>
-  <si>
-    <t>拍脸推送图</t>
   </si>
   <si>
     <t>shop</t>
@@ -2261,7 +2282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M202"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="26.875" customWidth="1"/>
@@ -3589,7 +3610,7 @@
       <c r="K91" s="1">
         <v>6</v>
       </c>
-      <c r="L91" s="8" t="s">
+      <c r="L91" s="10" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4520,8 +4541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" ht="15.75" spans="2:12">
-      <c r="B161" s="16"/>
+    <row r="161" ht="15.75" spans="9:12">
       <c r="I161" s="8" t="s">
         <v>321</v>
       </c>
@@ -4532,8 +4552,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" ht="15.75" spans="2:12">
-      <c r="B162" s="16"/>
+    <row r="162" ht="15.75" spans="9:12">
       <c r="I162" s="8" t="s">
         <v>323</v>
       </c>
@@ -4544,8 +4563,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" ht="15.75" spans="2:12">
-      <c r="B163" s="16"/>
+    <row r="163" ht="15.75" spans="9:12">
       <c r="I163" s="8" t="s">
         <v>325</v>
       </c>
@@ -4556,8 +4574,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" ht="15.75" spans="2:12">
-      <c r="B164" s="16"/>
+    <row r="164" ht="15.75" spans="9:12">
       <c r="I164" s="8" t="s">
         <v>327</v>
       </c>
@@ -4591,8 +4608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="166" ht="15.75" spans="2:12">
-      <c r="B166" s="16"/>
+    <row r="166" ht="15.75" spans="9:12">
       <c r="I166" s="8" t="s">
         <v>303</v>
       </c>
@@ -4603,8 +4619,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" ht="15.75" spans="2:12">
-      <c r="B167" s="16"/>
+    <row r="167" ht="15.75" spans="9:12">
       <c r="I167" s="8" t="s">
         <v>332</v>
       </c>
@@ -4615,8 +4630,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" ht="15.75" spans="2:12">
-      <c r="B168" s="16"/>
+    <row r="168" ht="15.75" spans="9:12">
       <c r="I168" s="8" t="s">
         <v>334</v>
       </c>
@@ -4627,8 +4641,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" ht="15.75" spans="2:12">
-      <c r="B169" s="16"/>
+    <row r="169" ht="15.75" spans="9:12">
       <c r="I169" s="8" t="s">
         <v>336</v>
       </c>
@@ -4639,8 +4652,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" ht="15.75" spans="2:12">
-      <c r="B170" s="16"/>
+    <row r="170" ht="15.75" spans="9:12">
       <c r="I170" s="8" t="s">
         <v>338</v>
       </c>
@@ -4651,8 +4663,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" ht="15.75" spans="2:12">
-      <c r="B171" s="16"/>
+    <row r="171" ht="15.75" spans="9:12">
       <c r="I171" s="8" t="s">
         <v>340</v>
       </c>
@@ -4663,8 +4674,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" ht="15.75" spans="2:12">
-      <c r="B172" s="16"/>
+    <row r="172" ht="15.75" spans="9:12">
       <c r="I172" s="8" t="s">
         <v>342</v>
       </c>
@@ -4675,8 +4685,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" ht="15.75" spans="2:12">
-      <c r="B173" s="16"/>
+    <row r="173" ht="15.75" spans="9:12">
       <c r="I173" s="8" t="s">
         <v>344</v>
       </c>
@@ -4710,8 +4719,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="175" spans="2:12">
-      <c r="B175" s="16"/>
+    <row r="175" spans="9:12">
       <c r="I175" t="s">
         <v>348</v>
       </c>
@@ -4722,8 +4730,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="2:12">
-      <c r="B176" s="16"/>
+    <row r="176" spans="9:12">
       <c r="I176" t="s">
         <v>305</v>
       </c>
@@ -4734,8 +4741,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="177" spans="2:12">
-      <c r="B177" s="16"/>
+    <row r="177" spans="9:12">
       <c r="I177" t="s">
         <v>340</v>
       </c>
@@ -4746,8 +4752,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="178" spans="2:12">
-      <c r="B178" s="16"/>
+    <row r="178" spans="9:12">
       <c r="I178" t="s">
         <v>344</v>
       </c>
@@ -4758,8 +4763,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="179" spans="2:12">
-      <c r="B179" s="16"/>
+    <row r="179" spans="9:12">
       <c r="I179" t="s">
         <v>353</v>
       </c>
@@ -4770,8 +4774,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="180" spans="2:12">
-      <c r="B180" s="16"/>
+    <row r="180" spans="9:12">
       <c r="I180" t="s">
         <v>355</v>
       </c>
@@ -4805,8 +4808,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="182" spans="2:12">
-      <c r="B182" s="16"/>
+    <row r="182" spans="9:12">
       <c r="I182" t="s">
         <v>359</v>
       </c>
@@ -4817,8 +4819,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="183" spans="2:12">
-      <c r="B183" s="16"/>
+    <row r="183" spans="9:12">
       <c r="I183" t="s">
         <v>361</v>
       </c>
@@ -4829,8 +4830,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="184" spans="2:12">
-      <c r="B184" s="16"/>
+    <row r="184" spans="9:12">
       <c r="I184" t="s">
         <v>363</v>
       </c>
@@ -4841,8 +4841,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="185" spans="2:12">
-      <c r="B185" s="16"/>
+    <row r="185" spans="9:12">
       <c r="I185" t="s">
         <v>365</v>
       </c>
@@ -4873,11 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L186" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="187" ht="15.75" spans="2:12">
-      <c r="B187" s="16"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" spans="9:12">
       <c r="I187" s="8" t="s">
         <v>292</v>
       </c>
@@ -4888,8 +4886,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="188" ht="15.75" spans="2:12">
-      <c r="B188" s="16"/>
+    <row r="188" ht="15.75" spans="9:12">
       <c r="I188" s="8" t="s">
         <v>370</v>
       </c>
@@ -4900,8 +4897,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="189" ht="15.75" spans="2:12">
-      <c r="B189" s="16"/>
+    <row r="189" ht="15.75" spans="9:12">
       <c r="I189" s="8" t="s">
         <v>372</v>
       </c>
@@ -4912,8 +4908,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="190" ht="15.75" spans="2:12">
-      <c r="B190" s="16"/>
+    <row r="190" ht="15.75" spans="9:12">
       <c r="I190" s="8" t="s">
         <v>374</v>
       </c>
@@ -4924,8 +4919,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" ht="15.75" spans="2:12">
-      <c r="B191" s="16"/>
+    <row r="191" ht="15.75" spans="9:12">
       <c r="I191" s="8" t="s">
         <v>376</v>
       </c>
@@ -4936,8 +4930,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="192" ht="15.75" spans="2:12">
-      <c r="B192" s="16"/>
+    <row r="192" ht="15.75" spans="9:12">
       <c r="I192" s="8" t="s">
         <v>378</v>
       </c>
@@ -4948,7 +4941,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="193" spans="2:12">
+    <row r="193" ht="15.75" spans="2:12">
       <c r="B193" s="5" t="s">
         <v>380</v>
       </c>
@@ -4967,72 +4960,129 @@
       <c r="K193" s="1">
         <v>0</v>
       </c>
-      <c r="L193" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="194" spans="9:12">
+      <c r="L193" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="194" ht="15.75" spans="9:12">
       <c r="I194" t="s">
         <v>382</v>
       </c>
       <c r="K194" s="1">
         <v>1</v>
       </c>
-      <c r="L194" t="s">
+      <c r="L194" s="8" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="195" spans="9:12">
+    <row r="195" ht="15.75" spans="5:12">
+      <c r="E195" s="16"/>
       <c r="I195" t="s">
+        <v>292</v>
+      </c>
+      <c r="K195" s="1">
+        <v>2</v>
+      </c>
+      <c r="L195" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="K195" s="1">
+    </row>
+    <row r="196" ht="15.75" spans="9:12">
+      <c r="I196" t="s">
+        <v>385</v>
+      </c>
+      <c r="K196" s="1">
+        <v>3</v>
+      </c>
+      <c r="L196" s="8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" spans="9:12">
+      <c r="I197" t="s">
+        <v>387</v>
+      </c>
+      <c r="K197" s="1">
+        <v>4</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" spans="2:12">
+      <c r="B198" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C198" t="b">
+        <v>0</v>
+      </c>
+      <c r="D198" t="b">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>390</v>
+      </c>
+      <c r="I198" t="s">
+        <v>23</v>
+      </c>
+      <c r="K198" s="1">
+        <v>0</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="199" spans="9:12">
+      <c r="I199" t="s">
+        <v>391</v>
+      </c>
+      <c r="K199" s="1">
         <v>101001</v>
       </c>
-      <c r="L195" s="9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="196" spans="9:12">
-      <c r="I196" t="s">
-        <v>386</v>
-      </c>
-      <c r="K196" s="1">
+      <c r="L199" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="200" spans="9:12">
+      <c r="I200" t="s">
+        <v>393</v>
+      </c>
+      <c r="K200" s="1">
         <v>101002</v>
       </c>
-      <c r="L196" s="9" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="197" spans="9:12">
-      <c r="I197" t="s">
-        <v>388</v>
-      </c>
-      <c r="K197" s="1">
+      <c r="L200" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="201" spans="9:12">
+      <c r="I201" t="s">
+        <v>395</v>
+      </c>
+      <c r="K201" s="1">
         <v>101003</v>
       </c>
-      <c r="L197" s="9" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="198" spans="8:12">
-      <c r="H198" s="17"/>
-      <c r="I198" s="17"/>
-      <c r="L198" s="18"/>
-    </row>
-    <row r="199" ht="15.75" spans="8:12">
-      <c r="H199" s="1"/>
-      <c r="I199" s="1"/>
-      <c r="L199" s="19"/>
-    </row>
-    <row r="200" ht="15.75" spans="12:12">
-      <c r="L200" s="19"/>
-    </row>
-    <row r="201" ht="15.75" spans="12:12">
-      <c r="L201" s="19"/>
-    </row>
-    <row r="202" ht="15.75" spans="12:12">
-      <c r="L202" s="19"/>
+      <c r="L201" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="202" spans="8:12">
+      <c r="H202" s="17"/>
+      <c r="I202" s="17"/>
+      <c r="L202" s="18"/>
+    </row>
+    <row r="203" ht="15.75" spans="8:12">
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="L203" s="19"/>
+    </row>
+    <row r="204" ht="15.75" spans="12:12">
+      <c r="L204" s="19"/>
+    </row>
+    <row r="205" ht="15.75" spans="12:12">
+      <c r="L205" s="19"/>
+    </row>
+    <row r="206" ht="15.75" spans="12:12">
+      <c r="L206" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
